--- a/Templates Converted/getDefaultAgenda.211207.xlsx
+++ b/Templates Converted/getDefaultAgenda.211207.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" state="visible" r:id="rId1"/>
@@ -210,6 +210,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -217,9 +220,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -609,19 +609,19 @@
           <t>Request Parameters</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
-      <c r="G1" s="14" t="n"/>
-      <c r="H1" s="14" t="n"/>
-      <c r="I1" s="14" t="n"/>
-      <c r="J1" s="14" t="n"/>
-      <c r="K1" s="14" t="n"/>
-      <c r="L1" s="14" t="n"/>
-      <c r="M1" s="14" t="n"/>
-      <c r="N1" s="14" t="n"/>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="15" t="n"/>
+      <c r="D1" s="15" t="n"/>
+      <c r="E1" s="15" t="n"/>
+      <c r="F1" s="15" t="n"/>
+      <c r="G1" s="15" t="n"/>
+      <c r="H1" s="15" t="n"/>
+      <c r="I1" s="15" t="n"/>
+      <c r="J1" s="15" t="n"/>
+      <c r="K1" s="15" t="n"/>
+      <c r="L1" s="15" t="n"/>
+      <c r="M1" s="15" t="n"/>
+      <c r="N1" s="15" t="n"/>
     </row>
     <row r="2" ht="57.6" customFormat="1" customHeight="1" s="4">
       <c r="A2" s="1" t="inlineStr">
@@ -629,7 +629,7 @@
           <t>Name</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -704,7 +704,7 @@
           <t>senderBIC</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>The BIC sending the request
 **ValidationRule(s)** It must be equal to the BIC of the DP certificate (errorCode XA02) 
@@ -753,15 +753,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFFF9999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
     <col width="19" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
@@ -889,43 +889,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>ErrorResponse</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -935,15 +898,15 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFFF9999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
     <col width="23" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
@@ -1071,43 +1034,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>ErrorResponse</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1121,13 +1047,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="14" customWidth="1" style="3" min="1" max="1"/>
-    <col width="49" customWidth="1" style="3" min="2" max="4"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" style="3" min="2" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
     <col width="18" customWidth="1" style="3" min="6" max="6"/>
     <col width="42" customWidth="1" style="3" min="7" max="7"/>
@@ -1139,7 +1065,6 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="63" customHeight="1">
@@ -1148,17 +1073,9 @@
           <t>Request Body</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>Structure of a FPAD account assessment request.</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
       <c r="E1" s="8" t="n"/>
       <c r="F1" s="8" t="n"/>
       <c r="G1" s="8" t="n"/>
@@ -1170,7 +1087,6 @@
       <c r="M1" s="8" t="n"/>
       <c r="N1" s="8" t="n"/>
       <c r="O1" s="8" t="n"/>
-      <c r="P1" s="12" t="n"/>
     </row>
     <row r="2" ht="43.15" customFormat="1" customHeight="1" s="4">
       <c r="A2" s="1" t="inlineStr">
@@ -1188,7 +1104,7 @@
           <t>Parent</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -1252,7 +1168,6 @@
           <t>Example</t>
         </is>
       </c>
-      <c r="P2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -1266,7 +1181,7 @@
         </is>
       </c>
       <c r="C3" s="12" t="n"/>
-      <c r="D3" s="16" t="n"/>
+      <c r="D3" s="12" t="n"/>
       <c r="E3" s="12" t="inlineStr">
         <is>
           <t>schema</t>
@@ -1290,100 +1205,6 @@
       <c r="M3" s="12" t="n"/>
       <c r="N3" s="12" t="n"/>
       <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>dateTime</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>The date and time of the API Request</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>settlementBIC</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>The STEP2 Settlement BIC owning liquidity position in CGS
-**ValidationRule(s)** It must correspond to one of the settlement BIC configured for the senderBIC, corresponding to the Preferred Agent (errorCode PY01)</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Bic11Only</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1 D3:D1048576">
@@ -1406,11 +1227,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="9" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
@@ -1422,6 +1243,31 @@
       <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Body</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>dateTime: '2019-06-21T23:20:50.000001'
+settlementBIC: IPSDID21XXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Bad Request</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>settlementBIC: IPSDID21XXX</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1279,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFD3ECB9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="24" customWidth="1" style="3" min="2" max="2"/>
-    <col width="24" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="59" customWidth="1" style="3" min="4" max="4"/>
+    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
     <col width="18" customWidth="1" style="3" min="6" max="6"/>
     <col width="42" customWidth="1" style="3" min="7" max="7"/>
@@ -1455,7 +1301,7 @@
     <col width="10" customWidth="1" style="3" min="13" max="13"/>
     <col width="15" customWidth="1" style="3" min="14" max="14"/>
     <col width="10" customWidth="1" style="3" min="15" max="15"/>
-    <col width="10" customWidth="1" style="3" min="16" max="16"/>
+    <col width="9.140625" customWidth="1" style="3" min="16" max="16"/>
     <col width="9.140625" customWidth="1" style="3" min="17" max="16384"/>
   </cols>
   <sheetData>
@@ -1487,7 +1333,6 @@
       <c r="M1" s="6" t="n"/>
       <c r="N1" s="6" t="n"/>
       <c r="O1" s="6" t="n"/>
-      <c r="P1" s="12" t="n"/>
     </row>
     <row r="2" ht="43.15" customFormat="1" customHeight="1" s="4">
       <c r="A2" s="1" t="inlineStr">
@@ -1569,7 +1414,6 @@
           <t>Example</t>
         </is>
       </c>
-      <c r="P2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -1607,508 +1451,6 @@
       <c r="M3" s="12" t="n"/>
       <c r="N3" s="12" t="n"/>
       <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>dateTime</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>The date and time of the API Response creation</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>settlementBIC</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>The STEP2 Settlement BIC owning liquidity position in CGS</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Bic11Only</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>defaultAgenda</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>object</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>defaultDailyThresholds</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>defaultAgenda</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>It must be present 5 times: 1 occurrence/day</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>DefaultDailyThresholds</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>defaultDailyThresholds</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>The day of the week</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>lacDefaultAgenda</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>defaultDailyThresholds</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>It must be present one occurrence/lac</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>SettlementBICs</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
-      <c r="P9" s="12" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>lacNumber</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>lacDefaultAgenda</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>The relevant LAC number</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>LacNumber</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>lowerPosition</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>lacDefaultAgenda</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>LAC-n lower position</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
-      <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="n"/>
-      <c r="O11" s="12" t="n"/>
-      <c r="P11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>basePosition</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>lacDefaultAgenda</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>LAC-n base position</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>upperPosition</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>lacDefaultAgenda</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>LAC-n upper position</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
-      <c r="P13" s="12" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>resetToBasePos</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>lacDefaultAgenda</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>Reset to base position option.
-Allowed values:
-- true
-- false</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2119,15 +1461,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFD3ECB9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
     <col width="12" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
@@ -2255,43 +1597,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>GetDefaultAgendaResponse</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2301,17 +1606,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFFF9999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="22" customWidth="1" style="3" min="2" max="2"/>
-    <col width="18" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="60" customWidth="1" style="3" min="4" max="4"/>
+    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="13" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
     <col width="18" customWidth="1" style="3" min="6" max="6"/>
     <col width="42" customWidth="1" style="3" min="7" max="7"/>
@@ -2323,7 +1628,7 @@
     <col width="10" customWidth="1" style="3" min="13" max="13"/>
     <col width="15" customWidth="1" style="3" min="14" max="14"/>
     <col width="10" customWidth="1" style="3" min="15" max="15"/>
-    <col width="10" customWidth="1" style="3" min="16" max="16"/>
+    <col width="9.140625" customWidth="1" style="3" min="16" max="16"/>
     <col width="9.140625" customWidth="1" style="3" min="17" max="16384"/>
   </cols>
   <sheetData>
@@ -2355,7 +1660,6 @@
       <c r="M1" s="6" t="n"/>
       <c r="N1" s="6" t="n"/>
       <c r="O1" s="6" t="n"/>
-      <c r="P1" s="12" t="n"/>
     </row>
     <row r="2" ht="43.15" customFormat="1" customHeight="1" s="4">
       <c r="A2" s="1" t="inlineStr">
@@ -2373,7 +1677,7 @@
           <t>Parent</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -2437,7 +1741,6 @@
           <t>Example</t>
         </is>
       </c>
-      <c r="P2" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -2451,7 +1754,7 @@
         </is>
       </c>
       <c r="C3" s="12" t="n"/>
-      <c r="D3" s="16" t="n"/>
+      <c r="D3" s="12" t="n"/>
       <c r="E3" s="12" t="inlineStr">
         <is>
           <t>schema</t>
@@ -2475,191 +1778,6 @@
       <c r="M3" s="12" t="n"/>
       <c r="N3" s="12" t="n"/>
       <c r="O3" s="12" t="n"/>
-      <c r="P3" s="12" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>dateTime</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>The date and time of the API Response creation</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n"/>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>DateTime</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="n"/>
-      <c r="K4" s="12" t="n"/>
-      <c r="L4" s="12" t="n"/>
-      <c r="M4" s="12" t="n"/>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n"/>
-      <c r="P4" s="12" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>errorCode</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>The relevant error code</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>ErrorCode</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
-      <c r="M5" s="12" t="n"/>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="12" t="n"/>
-      <c r="P5" s="12" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>errorCodeDescription</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>The description of the error</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>ErrorCodeDescription</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>requestId</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>The univocal reference per senderBIC and date assigned by the system to the API request</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>RequestId</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
-      <c r="M7" s="12" t="n"/>
-      <c r="N7" s="12" t="n"/>
-      <c r="O7" s="12" t="n"/>
-      <c r="P7" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2670,15 +1788,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFFF9999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
     <col width="14" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
@@ -2806,43 +1924,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>ErrorResponse</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2852,15 +1933,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFFF9999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
     <col width="11" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
@@ -2988,43 +2069,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>ErrorResponse</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -3034,15 +2078,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Foglio16">
-    <tabColor theme="9" tint="0.5999938962981048"/>
+    <tabColor rgb="FFFF9999"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="3" min="1" max="1"/>
-    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
     <col width="11" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
     <col width="13" customWidth="1" style="3" min="4" max="4"/>
     <col width="10" customWidth="1" style="3" min="5" max="5"/>
@@ -3170,43 +2214,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>content</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>application/json</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n"/>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>ErrorResponse</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="n"/>
-      <c r="K3" s="12" t="n"/>
-      <c r="L3" s="12" t="n"/>
-      <c r="M3" s="12" t="n"/>
-      <c r="N3" s="12" t="n"/>
-      <c r="O3" s="12" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
